--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R738bf58c2fd8432c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R33657b888d404db5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R33657b888d404db5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9bc7b26a6e854366"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9bc7b26a6e854366"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6ecacbef193446f5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6ecacbef193446f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re91e81b9bb364099"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re91e81b9bb364099"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R072c28e6cb8f45aa"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R072c28e6cb8f45aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9db3599497e9415b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9db3599497e9415b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R661063b3a79e4105"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R661063b3a79e4105"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8cc19856c08e4126"/>
   </x:sheets>
 </x:workbook>
 </file>
